--- a/src/test/resources/farmer-import/Template_list_of_farmers_other_countries_en.xlsx
+++ b/src/test/resources/farmer-import/Template_list_of_farmers_other_countries_en.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Javas\inatrace_frontend\src\assets\farmer-import\"/>
     </mc:Choice>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="566">
   <si>
     <t>List of farmers</t>
   </si>
@@ -1724,11 +1724,39 @@
   <si>
     <t>Geo Data (POLYGON((lat1 lon1, lat2 lon2,...)))</t>
   </si>
+  <si>
+    <t>Geo Data (POLYGON((lat1 lon1, lat2 lon2,...)), POINT(lat lon), GeoJSON, ODK/Kobo geoshape "lat lon alt acc;...", or P1(...)P2(...) for several plots)</t>
+  </si>
+  <si>
+    <t>GeoID (FAO) - identifier of the plot boundary in the FAO GeoID registry</t>
+  </si>
+  <si>
+    <t>8. The Geo Data column accepts any one of these formats - use whichever your GPS, GIS or data collection tool produced, there is no need to convert by hand:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a) WKT polygon or point, as documented before: POLYGON((lat_1 lon_1, lat_2 lon_2, ...)) or POINT(lat lon). Standard lon/lat WKT from QGIS or PostGIS is also understood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    b) ODK / KoboToolbox geoshape, geotrace or geopoint, copied straight out of the export: 5.1717367 10.2352433 1267.1 1.45;5.1718067 10.235235 1267.8 1.3;...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    c) GeoJSON: {"type":"Polygon","coordinates":[[[10.235,5.171],[10.236,5.172],[10.237,5.173],[10.235,5.171]]]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d) Several plots for one farmer: P1(&lt;geo data&gt;)P2(&lt;geo data&gt;), using any of the formats above inside each pair of brackets.</t>
+  </si>
+  <si>
+    <t>9. A farmer with more than one plot can also be spread over several rows: fill the farmer columns once, then put each extra plot on its own row leaving every other column empty.</t>
+  </si>
+  <si>
+    <t>10. The GeoID column takes the identifier of a plot boundary already registered with FAO (https://data.apps.fao.org/geoid). The boundary is fetched from the registry, so no coordinates are needed. If both columns are filled, the GeoID is used and the coordinates serve as a fallback if the registry cannot be reached.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3225,30 +3253,31 @@
   <dimension ref="A1:AM260"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="10" width="19.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="15" width="19.85546875" style="1" customWidth="1"/>
-    <col min="16" max="17" width="29.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="18.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="20.7109375" style="1" customWidth="1"/>
-    <col min="22" max="24" width="18.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="30.85546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="31.7109375" style="1" customWidth="1"/>
-    <col min="27" max="28" width="18.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="20.42578125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="26" style="1" customWidth="1"/>
-    <col min="31" max="31" width="21.140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="25.42578125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="22.7109375" style="1" customWidth="1"/>
-    <col min="34" max="34" width="29.5703125" style="1" customWidth="1"/>
-    <col min="35" max="40" width="8.7109375" style="1" customWidth="1"/>
-    <col min="41" max="16384" width="8.7109375" style="1"/>
+    <col min="36" max="40" customWidth="true" style="1" width="8.7109375"/>
+    <col min="1" max="1" customWidth="true" style="1" width="25.28515625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="17.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="26.140625"/>
+    <col min="4" max="4" customWidth="true" hidden="true" style="1" width="23.28515625"/>
+    <col min="5" max="5" customWidth="true" hidden="true" style="1" width="22.28515625"/>
+    <col min="6" max="10" customWidth="true" hidden="true" style="1" width="19.85546875"/>
+    <col min="11" max="15" customWidth="true" style="1" width="19.85546875"/>
+    <col min="16" max="17" customWidth="true" style="1" width="29.140625"/>
+    <col min="18" max="18" customWidth="true" style="1" width="17.140625"/>
+    <col min="19" max="19" customWidth="true" style="1" width="19.7109375"/>
+    <col min="20" max="20" customWidth="true" style="1" width="18.28515625"/>
+    <col min="21" max="21" customWidth="true" style="1" width="20.7109375"/>
+    <col min="22" max="24" customWidth="true" style="1" width="18.28515625"/>
+    <col min="25" max="25" customWidth="true" style="1" width="30.85546875"/>
+    <col min="26" max="26" customWidth="true" style="1" width="31.7109375"/>
+    <col min="27" max="28" customWidth="true" style="1" width="18.28515625"/>
+    <col min="29" max="29" customWidth="true" style="1" width="20.42578125"/>
+    <col min="30" max="30" customWidth="true" style="1" width="26.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="21.140625"/>
+    <col min="32" max="32" customWidth="true" style="1" width="25.42578125"/>
+    <col min="33" max="33" customWidth="true" style="1" width="22.7109375"/>
+    <col min="34" max="34" customWidth="true" style="1" width="29.5703125"/>
+    <col min="35" max="35" customWidth="true" style="1" width="29.5703125"/>
+    <col min="41" max="16384" style="1" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3518,9 +3547,11 @@
         <v>27</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>556</v>
-      </c>
-      <c r="AI5" s="3"/>
+        <v>557</v>
+      </c>
+      <c r="AI5" s="41" t="s">
+        <v>558</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
@@ -13995,10 +14026,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFE6B89-ECB2-0D4A-AAA6-245B33EAAB7C}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="161.85546875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="161.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -14046,7 +14077,37 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>555</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -14059,8 +14120,8 @@
   <dimension ref="A1:C270"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="67.28515625"/>
+    <col min="2" max="2" customWidth="true" width="23.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
